--- a/Plotting/Results_excels/production_shares_olefins_LowAmbition.xlsx
+++ b/Plotting/Results_excels/production_shares_olefins_LowAmbition.xlsx
@@ -539,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Conventional</t>
+          <t>Conventional (fossil)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Carbon Capture</t>
+          <t>Conventional (fossil) with CC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -620,22 +620,22 @@
         <v>1016974.754263447</v>
       </c>
       <c r="E6" t="n">
+        <v>1717666.256705123</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1290705.857411676</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1289650.900672308</v>
+      </c>
+      <c r="H6" t="n">
         <v>1717666.256705075</v>
       </c>
-      <c r="F6" t="n">
-        <v>1291315.402767987</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1289650.900672362</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1717666.256704899</v>
-      </c>
       <c r="I6" t="n">
-        <v>1290907.069595588</v>
+        <v>1290637.156899306</v>
       </c>
       <c r="J6" t="n">
-        <v>1289650.900680386</v>
+        <v>1289650.900672351</v>
       </c>
     </row>
     <row r="7">
@@ -691,19 +691,19 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>426262.425611852</v>
+        <v>426871.8445439408</v>
       </c>
       <c r="G8" t="n">
-        <v>427926.582477398</v>
+        <v>427926.5824774519</v>
       </c>
       <c r="H8" t="n">
-        <v>1.185345212715367e-09</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>426670.6740929194</v>
+        <v>426940.5308036975</v>
       </c>
       <c r="J8" t="n">
-        <v>427926.5824773965</v>
+        <v>427926.5824773986</v>
       </c>
     </row>
     <row r="9">
